--- a/assets/Pattern_Store_Group.xlsx
+++ b/assets/Pattern_Store_Group.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://earthboundtradingcom-my.sharepoint.com/personal/wesley_earthboundtrading_com/Documents/Desktop/EBT_AI_Project/Tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wesley\Documents\WebOrderAI\weborder-ai\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="23" documentId="8_{6D8E9985-D060-4357-BE57-E22F78CB3C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C8A15D1-8D7A-4698-BFE4-102E86C939D1}"/>
@@ -209,10 +209,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
